--- a/docs/exports/club/06650357_Dowels_Toastmasters_Club.xlsx
+++ b/docs/exports/club/06650357_Dowels_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -541,19 +541,19 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -637,22 +637,22 @@
         <v>10</v>
       </c>
       <c r="B7" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>23</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>54</v>
-      </c>
       <c r="E7" s="6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Out of 164 active clubs district-wide.</t>
+          <t>Out of 160 active clubs district-wide.</t>
         </is>
       </c>
     </row>
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-06-30  |  Report generated 04 Jul 2026, 13:24  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -734,11 +734,11 @@
         <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/06650357_Dowels_Toastmasters_Club.xlsx
+++ b/docs/exports/club/06650357_Dowels_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>1</v>
@@ -553,7 +553,7 @@
         <v>2</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -594,7 +594,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="6" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>24</v>
@@ -646,7 +646,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
@@ -693,7 +693,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:25  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>1</v>

--- a/docs/exports/club/06650357_Dowels_Toastmasters_Club.xlsx
+++ b/docs/exports/club/06650357_Dowels_Toastmasters_Club.xlsx
@@ -474,11 +474,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Level 2</t>
+          <t>Level 2 / OMM</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -554,6 +554,13 @@
       </c>
       <c r="E7" s="6" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Level 2 / OMM: from 2026-27, Toastmasters counts Online Meeting Mastery exploration completions toward the same DCP goals as Level 2 and reports them as one number, so the two can't be shown separately.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -571,7 +578,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
@@ -594,7 +601,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -613,7 +620,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Level 2 Rank</t>
+          <t>Level 2 / OMM Rank</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -693,7 +700,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:31  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>

--- a/docs/exports/club/06650357_Dowels_Toastmasters_Club.xlsx
+++ b/docs/exports/club/06650357_Dowels_Toastmasters_Club.xlsx
@@ -501,7 +501,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:44  |  District 82 Toastmasters Pathways Dashboard</t>
+          <t>Data as of 2026-10-20  |  Report generated 21 Oct 2026, 23:50  |  District 82 Toastmasters Pathways Dashboard</t>
         </is>
       </c>
     </row>
